--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -1036,13 +1036,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1099,13 +1099,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1125,13 +1125,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1188,13 +1188,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>6</v>
@@ -1214,13 +1214,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1277,13 +1277,13 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -1303,13 +1303,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1366,13 +1366,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>10</v>
@@ -1392,13 +1392,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1455,13 +1455,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1481,13 +1481,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1544,13 +1544,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1570,13 +1570,13 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1633,13 +1633,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1659,13 +1659,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1722,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1748,13 +1748,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1811,13 +1811,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>7</v>
@@ -1837,13 +1837,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1900,13 +1900,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1926,13 +1926,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1989,13 +1989,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -2015,13 +2015,13 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -2078,13 +2078,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -2104,13 +2104,13 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -2167,13 +2167,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2193,13 +2193,13 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -2256,13 +2256,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2345,13 +2345,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -2371,13 +2371,13 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>9</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2434,13 +2434,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2460,13 +2460,13 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2523,13 +2523,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2549,13 +2549,13 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>10</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2612,13 +2612,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2638,13 +2638,13 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>10</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2701,13 +2701,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2727,13 +2727,13 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>9</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2790,13 +2790,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>9</v>
@@ -2816,13 +2816,13 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>6</v>
@@ -2879,13 +2879,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>6</v>
@@ -2905,13 +2905,13 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>9</v>
@@ -2968,13 +2968,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>9</v>
@@ -2994,13 +2994,13 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -3057,13 +3057,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -3083,13 +3083,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -3146,13 +3146,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3172,13 +3172,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -3235,13 +3235,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3261,13 +3261,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -3324,13 +3324,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3350,13 +3350,13 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -3413,13 +3413,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>5</v>
@@ -3439,13 +3439,13 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>9</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -3502,13 +3502,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3528,13 +3528,13 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>7</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -3591,13 +3591,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3617,13 +3617,13 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>10</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3680,13 +3680,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -3706,13 +3706,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3769,13 +3769,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3795,13 +3795,13 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -3858,13 +3858,13 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>5</v>
@@ -3884,13 +3884,13 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C36">
         <v>10</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E36">
         <v>8</v>
@@ -3947,13 +3947,13 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z36">
         <v>8</v>
@@ -3973,13 +3973,13 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>10</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -4036,13 +4036,13 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>5</v>
@@ -4062,13 +4062,13 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>5</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -4125,13 +4125,13 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -4151,13 +4151,13 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>9</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -4214,13 +4214,13 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z39">
         <v>5</v>
@@ -4240,13 +4240,13 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>8</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -4303,13 +4303,13 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z40">
         <v>6</v>
@@ -4329,13 +4329,13 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>10</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -4392,13 +4392,13 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z41">
         <v>6</v>
@@ -4418,13 +4418,13 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>6</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -4481,13 +4481,13 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z42">
         <v>6</v>
@@ -4507,13 +4507,13 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>10</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>8</v>
@@ -4570,13 +4570,13 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>10</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z43">
         <v>8</v>
@@ -4596,13 +4596,13 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>6</v>
       </c>
       <c r="D44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E44">
         <v>6</v>
@@ -4659,13 +4659,13 @@
         <v>-1</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X44">
         <v>6</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z44">
         <v>6</v>
@@ -4807,13 +4807,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -4875,13 +4875,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -4943,13 +4943,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -5011,13 +5011,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>106.7</v>
@@ -5079,13 +5079,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>106.7</v>
@@ -5147,13 +5147,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -5215,13 +5215,13 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>80</v>
@@ -5283,13 +5283,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>80</v>
@@ -5351,13 +5351,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>106.7</v>
@@ -5419,13 +5419,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -5487,13 +5487,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -5555,13 +5555,13 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>106.7</v>
@@ -5623,13 +5623,13 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>106.7</v>
@@ -5691,13 +5691,13 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5759,13 +5759,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -5827,13 +5827,13 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>106.7</v>
@@ -5895,13 +5895,13 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -5963,13 +5963,13 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -6031,13 +6031,13 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>106.7</v>
@@ -6099,13 +6099,13 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -6167,13 +6167,13 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -6241,7 +6241,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -6303,13 +6303,13 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -6371,13 +6371,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C27">
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -6439,13 +6439,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -6507,13 +6507,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -6575,13 +6575,13 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -6643,13 +6643,13 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -6711,13 +6711,13 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>106.7</v>
@@ -6779,13 +6779,13 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>106.7</v>
@@ -6847,13 +6847,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>106.7</v>
@@ -6915,13 +6915,13 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>106.7</v>
@@ -6983,13 +6983,13 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>106.7</v>
@@ -7051,13 +7051,13 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>100</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>106.7</v>
@@ -7119,13 +7119,13 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C38">
         <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>106.7</v>
@@ -7187,13 +7187,13 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7255,13 +7255,13 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C40">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>106.7</v>
@@ -7323,13 +7323,13 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>100</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41">
         <v>106.7</v>
@@ -7391,13 +7391,13 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C42">
         <v>100</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>106.7</v>
@@ -7459,13 +7459,13 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>100</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>106.7</v>
@@ -7527,13 +7527,13 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C44">
         <v>100</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>106.7</v>
@@ -7642,7 +7642,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -7651,22 +7651,25 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>63.41</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>36.59</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7680,27 +7683,30 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>31.71</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -7709,19 +7715,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>63.41</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="G4">
-        <v>36.59</v>
+        <v>9.76</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7732,7 +7738,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -7741,19 +7747,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>90.23999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G5">
-        <v>9.76</v>
+        <v>7.32</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7764,7 +7770,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -7785,7 +7791,7 @@
         <v>7.32</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7796,7 +7802,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -7805,19 +7811,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>92.68000000000001</v>
+        <v>95.12</v>
       </c>
       <c r="G7">
-        <v>7.32</v>
+        <v>4.88</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7828,7 +7834,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7837,19 +7843,19 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>95.12</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7865,7 +7871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7890,1646 +7896,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920289</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920289</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920290</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920290</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920291</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920291</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920292</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920293</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920293</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920295</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920297</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920297</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920298</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920298</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920299</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920299</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920337</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920337</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920300</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920300</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920301</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920301</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920302</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920302</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920303</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920303</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920304</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920304</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920305</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920305</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" t="s">
-        <v>147</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920306</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920306</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920235</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920235</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920307</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920307</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920308</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920308</v>
-      </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920309</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920309</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920090</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920090</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920310</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>154</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920310</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" t="s">
-        <v>154</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920311</v>
-      </c>
-      <c r="B48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" t="s">
-        <v>155</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920311</v>
-      </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" t="s">
-        <v>155</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920313</v>
-      </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>88</v>
-      </c>
-      <c r="D50" t="s">
-        <v>156</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920313</v>
-      </c>
-      <c r="B51" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920314</v>
-      </c>
-      <c r="B52" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920314</v>
-      </c>
-      <c r="B53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" t="s">
-        <v>157</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920172</v>
-      </c>
-      <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>121</v>
-      </c>
-      <c r="D54" t="s">
-        <v>158</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920172</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>121</v>
-      </c>
-      <c r="D55" t="s">
-        <v>158</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920315</v>
-      </c>
-      <c r="B56" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D56" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920315</v>
-      </c>
-      <c r="B57" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920316</v>
-      </c>
-      <c r="B58" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" t="s">
-        <v>123</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920316</v>
-      </c>
-      <c r="B59" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" t="s">
-        <v>123</v>
-      </c>
-      <c r="D59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920317</v>
-      </c>
-      <c r="B60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920317</v>
-      </c>
-      <c r="B61" t="s">
-        <v>97</v>
-      </c>
-      <c r="C61" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920318</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" t="s">
-        <v>125</v>
-      </c>
-      <c r="D62" t="s">
-        <v>161</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920318</v>
-      </c>
-      <c r="B63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" t="s">
-        <v>161</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920319</v>
-      </c>
-      <c r="B64" t="s">
-        <v>98</v>
-      </c>
-      <c r="C64" t="s">
-        <v>107</v>
-      </c>
-      <c r="D64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920319</v>
-      </c>
-      <c r="B65" t="s">
-        <v>98</v>
-      </c>
-      <c r="C65" t="s">
-        <v>107</v>
-      </c>
-      <c r="D65" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920320</v>
-      </c>
-      <c r="B66" t="s">
-        <v>99</v>
-      </c>
-      <c r="C66" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" t="s">
-        <v>163</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920320</v>
-      </c>
-      <c r="B67" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" t="s">
-        <v>126</v>
-      </c>
-      <c r="D67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920321</v>
-      </c>
-      <c r="B68" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" t="s">
-        <v>127</v>
-      </c>
-      <c r="D68" t="s">
-        <v>164</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920321</v>
-      </c>
-      <c r="B69" t="s">
-        <v>99</v>
-      </c>
-      <c r="C69" t="s">
-        <v>127</v>
-      </c>
-      <c r="D69" t="s">
-        <v>164</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920323</v>
-      </c>
-      <c r="B70" t="s">
-        <v>100</v>
-      </c>
-      <c r="C70" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70" t="s">
-        <v>165</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920323</v>
-      </c>
-      <c r="B71" t="s">
-        <v>100</v>
-      </c>
-      <c r="C71" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" t="s">
-        <v>165</v>
-      </c>
-      <c r="E71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920324</v>
-      </c>
-      <c r="B72" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" t="s">
-        <v>128</v>
-      </c>
-      <c r="D72" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920324</v>
-      </c>
-      <c r="B73" t="s">
-        <v>101</v>
-      </c>
-      <c r="C73" t="s">
-        <v>128</v>
-      </c>
-      <c r="D73" t="s">
-        <v>166</v>
-      </c>
-      <c r="E73" t="s">
-        <v>5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920326</v>
-      </c>
-      <c r="B74" t="s">
-        <v>102</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74" t="s">
-        <v>167</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920326</v>
-      </c>
-      <c r="B75" t="s">
-        <v>102</v>
-      </c>
-      <c r="C75" t="s">
-        <v>98</v>
-      </c>
-      <c r="D75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920327</v>
-      </c>
-      <c r="B76" t="s">
-        <v>103</v>
-      </c>
-      <c r="C76" t="s">
-        <v>86</v>
-      </c>
-      <c r="D76" t="s">
-        <v>168</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920327</v>
-      </c>
-      <c r="B77" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" t="s">
-        <v>168</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920328</v>
-      </c>
-      <c r="B78" t="s">
-        <v>104</v>
-      </c>
-      <c r="C78" t="s">
-        <v>129</v>
-      </c>
-      <c r="D78" t="s">
-        <v>169</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920328</v>
-      </c>
-      <c r="B79" t="s">
-        <v>104</v>
-      </c>
-      <c r="C79" t="s">
-        <v>129</v>
-      </c>
-      <c r="D79" t="s">
-        <v>169</v>
-      </c>
-      <c r="E79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920329</v>
-      </c>
-      <c r="B80" t="s">
-        <v>105</v>
-      </c>
-      <c r="C80" t="s">
-        <v>130</v>
-      </c>
-      <c r="D80" t="s">
-        <v>170</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920329</v>
-      </c>
-      <c r="B81" t="s">
-        <v>105</v>
-      </c>
-      <c r="C81" t="s">
-        <v>130</v>
-      </c>
-      <c r="D81" t="s">
-        <v>170</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920330</v>
-      </c>
-      <c r="B82" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" t="s">
-        <v>131</v>
-      </c>
-      <c r="D82" t="s">
-        <v>171</v>
-      </c>
-      <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920330</v>
-      </c>
-      <c r="B83" t="s">
-        <v>106</v>
-      </c>
-      <c r="C83" t="s">
-        <v>131</v>
-      </c>
-      <c r="D83" t="s">
-        <v>171</v>
-      </c>
-      <c r="E83" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -9577,7 +7943,7 @@
         <v>132</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9594,7 +7960,7 @@
         <v>133</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9611,7 +7977,7 @@
         <v>134</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9628,7 +7994,7 @@
         <v>135</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9645,7 +8011,7 @@
         <v>136</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9662,7 +8028,7 @@
         <v>137</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9679,7 +8045,7 @@
         <v>138</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9696,7 +8062,7 @@
         <v>139</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9713,7 +8079,7 @@
         <v>140</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9730,7 +8096,7 @@
         <v>141</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9747,7 +8113,7 @@
         <v>142</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9764,7 +8130,7 @@
         <v>143</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9781,7 +8147,7 @@
         <v>144</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9798,7 +8164,7 @@
         <v>145</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9815,7 +8181,7 @@
         <v>146</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9832,7 +8198,7 @@
         <v>147</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9849,7 +8215,7 @@
         <v>148</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9866,7 +8232,7 @@
         <v>149</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9883,7 +8249,7 @@
         <v>150</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9900,7 +8266,7 @@
         <v>151</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9917,7 +8283,7 @@
         <v>152</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9934,7 +8300,7 @@
         <v>153</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9951,7 +8317,7 @@
         <v>154</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9968,7 +8334,7 @@
         <v>155</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9985,7 +8351,7 @@
         <v>156</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -10002,7 +8368,7 @@
         <v>157</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -10019,7 +8385,7 @@
         <v>158</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -10036,7 +8402,7 @@
         <v>159</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -10053,7 +8419,7 @@
         <v>156</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -10070,7 +8436,7 @@
         <v>160</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -10087,7 +8453,7 @@
         <v>161</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -10104,7 +8470,7 @@
         <v>162</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -10121,7 +8487,7 @@
         <v>163</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -10138,7 +8504,7 @@
         <v>164</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -10155,7 +8521,7 @@
         <v>165</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -10172,7 +8538,7 @@
         <v>166</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -10189,7 +8555,7 @@
         <v>167</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -10206,7 +8572,7 @@
         <v>168</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -10223,7 +8589,7 @@
         <v>169</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -10240,7 +8606,7 @@
         <v>170</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -10257,7 +8623,7 @@
         <v>171</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10267,7 +8633,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -10299,16 +8665,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920289</v>
+        <v>21330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -10317,44 +8683,44 @@
         <v>66</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920289</v>
+        <v>21330051920298</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920290</v>
+        <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -10363,44 +8729,44 @@
         <v>66</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920290</v>
+        <v>21330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>66</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920291</v>
+        <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -10409,44 +8775,44 @@
         <v>66</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920291</v>
+        <v>21330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920295</v>
+        <v>21330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -10455,44 +8821,44 @@
         <v>66</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920295</v>
+        <v>21330051920316</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>66</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920297</v>
+        <v>21330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -10501,44 +8867,44 @@
         <v>66</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920297</v>
+        <v>21330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>66</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920301</v>
+        <v>21330051920323</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -10547,44 +8913,44 @@
         <v>66</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920301</v>
+        <v>21330051920323</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920302</v>
+        <v>21330051920289</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -10593,812 +8959,260 @@
         <v>66</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920302</v>
+        <v>21330051920292</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>66</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920304</v>
+        <v>21330051920293</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>66</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920304</v>
+        <v>21330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>66</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920306</v>
+        <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B19" t="s">
         <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920235</v>
+        <v>21330051920310</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920235</v>
+        <v>21330051920311</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>66</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920307</v>
+        <v>21330051920313</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920307</v>
+        <v>21330051920315</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920309</v>
+        <v>21330051920319</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920309</v>
+        <v>21330051920330</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>66</v>
       </c>
       <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920090</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920090</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920314</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920314</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920172</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920172</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920315</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920315</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920317</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920317</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920318</v>
-      </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920318</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>125</v>
-      </c>
-      <c r="D37" t="s">
-        <v>161</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920320</v>
-      </c>
-      <c r="B38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920320</v>
-      </c>
-      <c r="B39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920326</v>
-      </c>
-      <c r="B40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920326</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920327</v>
-      </c>
-      <c r="B42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920327</v>
-      </c>
-      <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920328</v>
-      </c>
-      <c r="B44" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" t="s">
-        <v>169</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>66</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920328</v>
-      </c>
-      <c r="B45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" t="s">
-        <v>169</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920329</v>
-      </c>
-      <c r="B46" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920329</v>
-      </c>
-      <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920330</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" t="s">
-        <v>131</v>
-      </c>
-      <c r="D48" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920330</v>
-      </c>
-      <c r="B49" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -219,7 +219,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>NC</t>
@@ -7677,7 +7692,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>41</v>
@@ -7709,7 +7724,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>41</v>
@@ -7741,7 +7756,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>41</v>
@@ -7773,7 +7788,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -7805,7 +7820,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -7837,7 +7852,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>41</v>
@@ -7880,16 +7895,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7914,16 +7929,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>64</v>
@@ -7934,13 +7949,13 @@
         <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7951,13 +7966,13 @@
         <v>21330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7968,13 +7983,13 @@
         <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7985,13 +8000,13 @@
         <v>21330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -8002,13 +8017,13 @@
         <v>21330051920293</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -8019,13 +8034,13 @@
         <v>21330051920295</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8036,13 +8051,13 @@
         <v>21330051920297</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8053,13 +8068,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8070,13 +8085,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8087,13 +8102,13 @@
         <v>21330051920337</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -8104,13 +8119,13 @@
         <v>21330051920300</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -8121,13 +8136,13 @@
         <v>21330051920301</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -8138,13 +8153,13 @@
         <v>21330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -8155,13 +8170,13 @@
         <v>21330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -8172,13 +8187,13 @@
         <v>21330051920304</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -8189,13 +8204,13 @@
         <v>21330051920305</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -8206,13 +8221,13 @@
         <v>21330051920306</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8223,13 +8238,13 @@
         <v>20330051920235</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -8240,13 +8255,13 @@
         <v>21330051920307</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -8257,13 +8272,13 @@
         <v>21330051920308</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -8274,13 +8289,13 @@
         <v>21330051920309</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -8291,13 +8306,13 @@
         <v>21330051920090</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -8308,13 +8323,13 @@
         <v>21330051920310</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -8325,13 +8340,13 @@
         <v>21330051920311</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -8342,13 +8357,13 @@
         <v>21330051920313</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -8359,13 +8374,13 @@
         <v>21330051920314</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -8376,13 +8391,13 @@
         <v>21330051920172</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -8393,13 +8408,13 @@
         <v>21330051920315</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -8410,13 +8425,13 @@
         <v>21330051920316</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -8427,13 +8442,13 @@
         <v>21330051920317</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -8444,13 +8459,13 @@
         <v>21330051920318</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -8461,13 +8476,13 @@
         <v>21330051920319</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -8478,13 +8493,13 @@
         <v>21330051920320</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -8495,13 +8510,13 @@
         <v>21330051920321</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -8512,13 +8527,13 @@
         <v>21330051920323</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -8529,13 +8544,13 @@
         <v>21330051920324</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -8546,13 +8561,13 @@
         <v>21330051920326</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -8563,13 +8578,13 @@
         <v>21330051920327</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -8580,13 +8595,13 @@
         <v>21330051920328</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -8597,13 +8612,13 @@
         <v>21330051920329</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -8614,13 +8629,13 @@
         <v>21330051920330</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -8642,16 +8657,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8668,19 +8683,19 @@
         <v>21330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8691,13 +8706,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8714,19 +8729,19 @@
         <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8737,13 +8752,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8760,19 +8775,19 @@
         <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8783,13 +8798,13 @@
         <v>21330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8806,19 +8821,19 @@
         <v>21330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8829,13 +8844,13 @@
         <v>21330051920316</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -8852,19 +8867,19 @@
         <v>21330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8875,13 +8890,13 @@
         <v>21330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -8898,19 +8913,19 @@
         <v>21330051920323</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8921,13 +8936,13 @@
         <v>21330051920323</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -8944,19 +8959,19 @@
         <v>21330051920289</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8967,19 +8982,19 @@
         <v>21330051920292</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8990,13 +9005,13 @@
         <v>21330051920293</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -9013,13 +9028,13 @@
         <v>21330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -9036,13 +9051,13 @@
         <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -9059,19 +9074,19 @@
         <v>20330051920235</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -9082,13 +9097,13 @@
         <v>21330051920310</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -9105,13 +9120,13 @@
         <v>21330051920311</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -9128,13 +9143,13 @@
         <v>21330051920313</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -9151,19 +9166,19 @@
         <v>21330051920315</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -9174,13 +9189,13 @@
         <v>21330051920319</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -9197,19 +9212,19 @@
         <v>21330051920330</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25">
         <v>5</v>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -219,12 +218,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
@@ -249,234 +248,132 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
     <t>AMY JULIET</t>
   </si>
   <si>
     <t>LUIS CARLOS</t>
   </si>
   <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
@@ -489,64 +386,22 @@
     <t>DIANA CRISTINA</t>
   </si>
   <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>ADAL</t>
-  </si>
-  <si>
     <t>OLIVA</t>
   </si>
   <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
     <t>ROSA JAZMIN</t>
   </si>
   <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
     <t>SAYURI BETSABE</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
     <t>DIEGO EMILIO</t>
   </si>
   <si>
-    <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
     <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>LIZETH</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -556,6 +411,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -608,11 +466,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1081,16 +940,16 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1114,7 +973,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1126,13 +985,13 @@
         <v>7</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1161,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1170,16 +1029,16 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1215,13 +1074,13 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1250,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1259,16 +1118,16 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1307,10 +1166,10 @@
         <v>10</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1339,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1348,16 +1207,16 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1393,13 +1252,13 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1428,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1437,16 +1296,16 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1470,7 +1329,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1485,10 +1344,10 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1517,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1526,16 +1385,16 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1571,13 +1430,13 @@
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1606,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1615,16 +1474,16 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1660,10 +1519,10 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1695,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1704,16 +1563,16 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1737,7 +1596,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1749,10 +1608,10 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1784,7 +1643,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1793,16 +1652,16 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1841,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1873,7 +1732,7 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1882,16 +1741,16 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1930,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1962,7 +1821,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1971,16 +1830,16 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -2019,10 +1878,10 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -2051,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -2060,16 +1919,16 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2093,7 +1952,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -2102,7 +1961,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -2140,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -2149,16 +2008,16 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2197,10 +2056,10 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2229,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2238,16 +2097,16 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2318,7 +2177,7 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2327,16 +2186,16 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2375,7 +2234,7 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2407,7 +2266,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2416,16 +2275,16 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2461,13 +2320,13 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2496,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2505,16 +2364,16 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2538,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2547,13 +2406,13 @@
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2585,7 +2444,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2594,16 +2453,16 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2639,13 +2498,13 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2674,7 +2533,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2683,16 +2542,16 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2716,7 +2575,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2728,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2763,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2772,16 +2631,16 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2805,7 +2664,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2814,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2852,7 +2711,7 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2861,16 +2720,16 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2894,7 +2753,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2903,7 +2762,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2941,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2950,16 +2809,16 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2992,7 +2851,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -3030,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -3039,16 +2898,16 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3072,7 +2931,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -3084,10 +2943,10 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3119,7 +2978,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -3128,16 +2987,16 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3161,7 +3020,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -3170,13 +3029,13 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3208,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -3217,16 +3076,16 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3259,13 +3118,13 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>10</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3297,7 +3156,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -3306,16 +3165,16 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3354,7 +3213,7 @@
         <v>10</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3386,7 +3245,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3395,16 +3254,16 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3475,7 +3334,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3484,16 +3343,16 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3526,16 +3385,16 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3564,7 +3423,7 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3573,16 +3432,16 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3606,7 +3465,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3621,10 +3480,10 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3653,7 +3512,7 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3662,16 +3521,16 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3704,7 +3563,7 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3742,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3751,16 +3610,16 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3784,7 +3643,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3793,13 +3652,13 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>10</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>8</v>
@@ -3831,7 +3690,7 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3840,16 +3699,16 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3873,7 +3732,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3920,7 +3779,7 @@
         <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3929,16 +3788,16 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3971,16 +3830,16 @@
         <v>8</v>
       </c>
       <c r="Z36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36">
         <v>10</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4009,7 +3868,7 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -4018,16 +3877,16 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4063,10 +3922,10 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>8</v>
@@ -4098,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -4107,16 +3966,16 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4187,7 +4046,7 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -4196,16 +4055,16 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4238,16 +4097,16 @@
         <v>8</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4276,7 +4135,7 @@
         <v>7</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -4285,16 +4144,16 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4327,13 +4186,13 @@
         <v>9</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC40">
         <v>7</v>
@@ -4365,7 +4224,7 @@
         <v>8</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
         <v>-1</v>
@@ -4374,16 +4233,16 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4407,7 +4266,7 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -4416,16 +4275,16 @@
         <v>8</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41">
         <v>10</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC41">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4454,7 +4313,7 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J42">
         <v>-1</v>
@@ -4463,16 +4322,16 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4496,7 +4355,7 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X42">
         <v>6</v>
@@ -4505,16 +4364,16 @@
         <v>8</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -4543,7 +4402,7 @@
         <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -4552,16 +4411,16 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4594,7 +4453,7 @@
         <v>8</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43">
         <v>10</v>
@@ -4603,7 +4462,7 @@
         <v>10</v>
       </c>
       <c r="AC43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -4632,7 +4491,7 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J44">
         <v>-1</v>
@@ -4641,16 +4500,16 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4689,7 +4548,7 @@
         <v>9</v>
       </c>
       <c r="AB44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC44">
         <v>7</v>
@@ -4843,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4852,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -4911,7 +4770,7 @@
         <v>96.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4920,16 +4779,16 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -4979,7 +4838,7 @@
         <v>96.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4988,16 +4847,16 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -5047,7 +4906,7 @@
         <v>93.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -5056,16 +4915,16 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -5115,7 +4974,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -5124,16 +4983,16 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -5183,7 +5042,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -5192,16 +5051,16 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -5251,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -5260,16 +5119,16 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -5319,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -5328,16 +5187,16 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -5387,7 +5246,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -5396,16 +5255,16 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -5455,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -5464,16 +5323,16 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -5523,7 +5382,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -5532,16 +5391,16 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -5591,7 +5450,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -5600,16 +5459,16 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -5659,7 +5518,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -5668,16 +5527,16 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -5795,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -5804,16 +5663,16 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5863,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -5872,16 +5731,16 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5931,7 +5790,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -5940,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5999,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -6008,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -6067,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -6076,16 +5935,16 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -6135,7 +5994,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -6144,16 +6003,16 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -6203,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -6212,16 +6071,16 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6339,7 +6198,7 @@
         <v>96.7</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -6348,16 +6207,16 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6407,7 +6266,7 @@
         <v>96.7</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -6416,16 +6275,16 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6475,7 +6334,7 @@
         <v>96.7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -6484,16 +6343,16 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6543,7 +6402,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -6552,16 +6411,16 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6611,7 +6470,7 @@
         <v>96.7</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -6620,16 +6479,16 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -6679,7 +6538,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -6688,16 +6547,16 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -6747,7 +6606,7 @@
         <v>96.7</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -6756,16 +6615,16 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -6815,7 +6674,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -6824,16 +6683,16 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -6883,7 +6742,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -6892,16 +6751,16 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -6951,7 +6810,7 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -6960,16 +6819,16 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -7019,7 +6878,7 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -7028,16 +6887,16 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -7087,7 +6946,7 @@
         <v>96.7</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -7096,16 +6955,16 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -7155,7 +7014,7 @@
         <v>66.7</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -7164,16 +7023,16 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -7223,7 +7082,7 @@
         <v>96.7</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -7232,16 +7091,16 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -7291,7 +7150,7 @@
         <v>96.7</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -7300,16 +7159,16 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -7359,7 +7218,7 @@
         <v>96.7</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -7368,16 +7227,16 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -7427,7 +7286,7 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -7436,16 +7295,16 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -7495,7 +7354,7 @@
         <v>100</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -7504,16 +7363,16 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -7563,7 +7422,7 @@
         <v>100</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -7572,16 +7431,16 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -7621,6 +7480,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -7657,7 +7518,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -7666,30 +7527,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>63.41</v>
-      </c>
-      <c r="G2">
-        <v>36.59</v>
+        <v>17</v>
+      </c>
+      <c r="F2" s="2">
+        <v>58.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>41.5</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7698,30 +7559,30 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>13</v>
-      </c>
-      <c r="F3">
-        <v>68.29000000000001</v>
-      </c>
-      <c r="G3">
-        <v>31.71</v>
+        <v>15</v>
+      </c>
+      <c r="F3" s="2">
+        <v>63.4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>36.6</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7735,28 +7596,28 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="G4">
-        <v>9.76</v>
+      <c r="F4" s="2">
+        <v>90.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>41</v>
@@ -7767,28 +7628,28 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="G5">
-        <v>7.32</v>
+      <c r="F5" s="2">
+        <v>92.7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -7799,19 +7660,19 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="G6">
-        <v>7.32</v>
+      <c r="F6" s="2">
+        <v>92.7</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.3</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7831,11 +7692,11 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
-        <v>95.12</v>
-      </c>
-      <c r="G7">
-        <v>4.88</v>
+      <c r="F7" s="2">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4.9</v>
       </c>
       <c r="H7">
         <v>8.699999999999999</v>
@@ -7843,7 +7704,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7863,10 +7724,10 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
@@ -7875,7 +7736,7 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7920,735 +7781,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920289</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920290</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920293</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920295</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920297</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920298</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920299</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920337</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920300</v>
-      </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920304</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920306</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920235</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920307</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920308</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920309</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920090</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920311</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" t="s">
-        <v>160</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920313</v>
-      </c>
-      <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920314</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920315</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>164</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920316</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920317</v>
-      </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920318</v>
-      </c>
-      <c r="B32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051920319</v>
-      </c>
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>21330051920320</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>21330051920321</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>21330051920323</v>
-      </c>
-      <c r="B36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>21330051920324</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>21330051920326</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" t="s">
-        <v>172</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>21330051920327</v>
-      </c>
-      <c r="B39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>173</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>21330051920328</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>21330051920329</v>
-      </c>
-      <c r="B41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>21330051920330</v>
-      </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8683,19 +7816,19 @@
         <v>21330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8706,19 +7839,19 @@
         <v>21330051920298</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8726,22 +7859,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920299</v>
+        <v>21330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8749,22 +7882,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920299</v>
+        <v>21330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8772,22 +7905,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920337</v>
+        <v>21330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8795,22 +7928,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920337</v>
+        <v>21330051920321</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8818,22 +7951,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920316</v>
+        <v>21330051920328</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8841,22 +7974,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920316</v>
+        <v>21330051920328</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8864,22 +7997,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920321</v>
+        <v>21330051920289</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8887,22 +8020,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920321</v>
+        <v>21330051920293</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8910,19 +8043,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920323</v>
+        <v>21330051920299</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>67</v>
@@ -8933,22 +8066,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920323</v>
+        <v>21330051920300</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8956,22 +8089,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920289</v>
+        <v>21330051920301</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8979,22 +8112,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920292</v>
+        <v>21330051920305</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -9002,19 +8135,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920293</v>
+        <v>21330051920306</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
         <v>66</v>
@@ -9025,19 +8158,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920300</v>
+        <v>20330051920235</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>66</v>
@@ -9048,19 +8181,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920305</v>
+        <v>21330051920307</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
@@ -9071,22 +8204,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920235</v>
+        <v>21330051920090</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -9094,22 +8227,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920310</v>
+        <v>21330051920313</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -9117,19 +8250,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920311</v>
+        <v>21330051920315</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>66</v>
@@ -9140,22 +8273,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920313</v>
+        <v>21330051920316</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -9163,19 +8296,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920315</v>
+        <v>21330051920319</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
@@ -9186,19 +8319,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920319</v>
+        <v>21330051920323</v>
       </c>
       <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
         <v>103</v>
       </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
@@ -9209,24 +8342,47 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920330</v>
+        <v>21330051920326</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>67</v>
       </c>
       <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920330</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
   <si>
     <t>Materia</t>
   </si>
@@ -224,15 +224,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
@@ -257,9 +257,6 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -311,9 +308,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -354,9 +348,6 @@
   </si>
   <si>
     <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
   </si>
   <si>
     <t>ANDRES</t>
@@ -934,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1023,7 +1014,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1112,7 +1103,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1201,7 +1192,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1290,7 +1281,7 @@
         <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1332,7 +1323,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1379,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1468,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1557,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1599,7 +1590,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1646,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1735,7 +1726,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1824,7 +1815,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1913,7 +1904,7 @@
         <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -2002,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2091,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2133,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2180,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2222,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2269,7 +2260,7 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2311,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2358,7 +2349,7 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2400,7 +2391,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2447,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2489,7 +2480,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2536,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2625,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2714,7 +2705,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2756,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2803,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2892,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2934,7 +2925,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2981,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -3070,7 +3061,7 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3159,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3248,7 +3239,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3290,7 +3281,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3337,7 +3328,7 @@
         <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3379,7 +3370,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3426,7 +3417,7 @@
         <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3468,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3515,7 +3506,7 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3557,7 +3548,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3604,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3693,7 +3684,7 @@
         <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3735,7 +3726,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3782,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3871,7 +3862,7 @@
         <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3960,7 +3951,7 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -4049,7 +4040,7 @@
         <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -4091,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -4138,7 +4129,7 @@
         <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -4180,7 +4171,7 @@
         <v>6</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>9</v>
@@ -4227,7 +4218,7 @@
         <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -4316,7 +4307,7 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -4358,7 +4349,7 @@
         <v>5</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4405,7 +4396,7 @@
         <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
         <v>-1</v>
@@ -4494,7 +4485,7 @@
         <v>5</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
         <v>-1</v>
@@ -4536,7 +4527,7 @@
         <v>5</v>
       </c>
       <c r="X44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -4705,7 +4696,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -4773,7 +4764,7 @@
         <v>95</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -4841,7 +4832,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -4909,7 +4900,7 @@
         <v>95</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -4977,7 +4968,7 @@
         <v>90</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -5045,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -5113,7 +5104,7 @@
         <v>80</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5181,7 +5172,7 @@
         <v>80</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -5249,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -5317,7 +5308,7 @@
         <v>90</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -5385,7 +5376,7 @@
         <v>80</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -5453,7 +5444,7 @@
         <v>95</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -5521,7 +5512,7 @@
         <v>95</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -5657,7 +5648,7 @@
         <v>90</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -5725,7 +5716,7 @@
         <v>85</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -5793,7 +5784,7 @@
         <v>85</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -5861,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -5929,7 +5920,7 @@
         <v>90</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -5997,7 +5988,7 @@
         <v>90</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -6065,7 +6056,7 @@
         <v>95</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6201,7 +6192,7 @@
         <v>90</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -6269,7 +6260,7 @@
         <v>95</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -6337,7 +6328,7 @@
         <v>90</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -6405,7 +6396,7 @@
         <v>90</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -6473,7 +6464,7 @@
         <v>80</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -6541,7 +6532,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -6609,7 +6600,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -6677,7 +6668,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -6745,7 +6736,7 @@
         <v>90</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -6813,7 +6804,7 @@
         <v>90</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6881,7 +6872,7 @@
         <v>95</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -6949,7 +6940,7 @@
         <v>90</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -7017,7 +7008,7 @@
         <v>75</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -7085,7 +7076,7 @@
         <v>75</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -7153,7 +7144,7 @@
         <v>90</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -7221,7 +7212,7 @@
         <v>95</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -7289,7 +7280,7 @@
         <v>75</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -7357,7 +7348,7 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -7425,7 +7416,7 @@
         <v>85</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -7582,7 +7573,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7603,7 +7594,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7614,7 +7605,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -7623,19 +7614,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
       <c r="G5" s="2">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7646,10 +7637,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -7667,7 +7658,7 @@
         <v>7.3</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7678,28 +7669,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>41</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>95.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="G7" s="2">
-        <v>4.9</v>
+        <v>7.3</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7781,7 +7772,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7819,10 +7810,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7842,10 +7833,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7865,10 +7856,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7888,10 +7879,10 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -7911,10 +7902,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7934,10 +7925,10 @@
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7951,16 +7942,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920328</v>
+        <v>21330051920289</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7974,16 +7965,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920328</v>
+        <v>21330051920293</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
         <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7997,22 +7988,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920289</v>
+        <v>21330051920299</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8020,16 +8011,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920293</v>
+        <v>21330051920300</v>
       </c>
       <c r="B11" t="s">
         <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -8043,22 +8034,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920299</v>
+        <v>21330051920301</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8066,16 +8057,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920300</v>
+        <v>21330051920305</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -8089,16 +8080,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920301</v>
+        <v>21330051920306</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -8112,22 +8103,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920305</v>
+        <v>20330051920235</v>
       </c>
       <c r="B15" t="s">
         <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8135,16 +8126,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920306</v>
+        <v>21330051920307</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -8158,16 +8149,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920235</v>
+        <v>21330051920090</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -8181,22 +8172,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920307</v>
+        <v>21330051920313</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8204,16 +8195,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920090</v>
+        <v>21330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -8227,16 +8218,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920313</v>
+        <v>21330051920316</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
         <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -8250,22 +8241,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920315</v>
+        <v>21330051920319</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -8273,22 +8264,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920316</v>
+        <v>21330051920323</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8296,16 +8287,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920319</v>
+        <v>21330051920326</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -8319,16 +8310,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920323</v>
+        <v>21330051920330</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -8337,52 +8328,6 @@
         <v>66</v>
       </c>
       <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920326</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920330</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -928,7 +928,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -1017,7 +1017,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1106,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1195,7 +1195,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1373,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1462,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1551,7 +1551,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1640,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1729,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1996,7 +1996,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2174,7 +2174,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -2263,7 +2263,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -2352,7 +2352,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2441,7 +2441,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2530,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -2619,7 +2619,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2708,7 +2708,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2797,7 +2797,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2886,7 +2886,7 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -2975,7 +2975,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -3064,7 +3064,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -3153,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>6</v>
@@ -3242,7 +3242,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -3331,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3509,7 +3509,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>7</v>
@@ -3687,7 +3687,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -3776,7 +3776,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3865,7 +3865,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>6</v>
@@ -3954,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -4043,7 +4043,7 @@
         <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -4132,7 +4132,7 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -4221,7 +4221,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
         <v>8</v>
@@ -4310,7 +4310,7 @@
         <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -4399,7 +4399,7 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L43">
         <v>10</v>
@@ -4488,7 +4488,7 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -4699,7 +4699,7 @@
         <v>120</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>106.7</v>
@@ -4767,7 +4767,7 @@
         <v>120</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>106.7</v>
@@ -4835,7 +4835,7 @@
         <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>106.7</v>
@@ -4903,7 +4903,7 @@
         <v>120</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>106.7</v>
@@ -4971,7 +4971,7 @@
         <v>120</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>106.7</v>
@@ -5039,7 +5039,7 @@
         <v>120</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>106.7</v>
@@ -5107,7 +5107,7 @@
         <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>80</v>
@@ -5175,7 +5175,7 @@
         <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>80</v>
@@ -5243,7 +5243,7 @@
         <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>106.7</v>
@@ -5311,7 +5311,7 @@
         <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>106.7</v>
@@ -5379,7 +5379,7 @@
         <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>106.7</v>
@@ -5447,7 +5447,7 @@
         <v>120</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>106.7</v>
@@ -5515,7 +5515,7 @@
         <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>106.7</v>
@@ -5583,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>106.7</v>
@@ -5719,7 +5719,7 @@
         <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>106.7</v>
@@ -5787,7 +5787,7 @@
         <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>106.7</v>
@@ -5855,7 +5855,7 @@
         <v>120</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>106.7</v>
@@ -5923,7 +5923,7 @@
         <v>120</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>106.7</v>
@@ -5991,7 +5991,7 @@
         <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>106.7</v>
@@ -6059,7 +6059,7 @@
         <v>120</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>106.7</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6195,7 +6195,7 @@
         <v>120</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>106.7</v>
@@ -6263,7 +6263,7 @@
         <v>120</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>106.7</v>
@@ -6331,7 +6331,7 @@
         <v>120</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>106.7</v>
@@ -6399,7 +6399,7 @@
         <v>120</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>106.7</v>
@@ -6467,7 +6467,7 @@
         <v>120</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>106.7</v>
@@ -6535,7 +6535,7 @@
         <v>120</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>106.7</v>
@@ -6603,7 +6603,7 @@
         <v>120</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>106.7</v>
@@ -6671,7 +6671,7 @@
         <v>120</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>106.7</v>
@@ -6739,7 +6739,7 @@
         <v>120</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>106.7</v>
@@ -6807,7 +6807,7 @@
         <v>120</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>93.3</v>
@@ -6875,7 +6875,7 @@
         <v>120</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>106.7</v>
@@ -6943,7 +6943,7 @@
         <v>120</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>106.7</v>
@@ -7011,7 +7011,7 @@
         <v>120</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>66.7</v>
@@ -7079,7 +7079,7 @@
         <v>120</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>106.7</v>
@@ -7147,7 +7147,7 @@
         <v>120</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>80</v>
@@ -7215,7 +7215,7 @@
         <v>120</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>106.7</v>
@@ -7283,7 +7283,7 @@
         <v>120</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42">
         <v>86.7</v>
@@ -7351,7 +7351,7 @@
         <v>120</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43">
         <v>106.7</v>
@@ -7419,7 +7419,7 @@
         <v>120</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44">
         <v>106.7</v>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -4681,7 +4681,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -4696,16 +4696,16 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -4714,25 +4714,25 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4749,7 +4749,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -4764,16 +4764,16 @@
         <v>95</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>97.09999999999999</v>
@@ -4782,25 +4782,25 @@
         <v>96.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4817,7 +4817,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -4829,46 +4829,46 @@
         <v>96.7</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4885,7 +4885,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -4897,46 +4897,46 @@
         <v>93.3</v>
       </c>
       <c r="I7">
+        <v>90</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="O7">
         <v>95</v>
       </c>
-      <c r="J7">
-        <v>120</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="L7">
-        <v>106.7</v>
-      </c>
-      <c r="M7">
-        <v>120</v>
-      </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>96.7</v>
-      </c>
       <c r="P7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4953,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4965,46 +4965,46 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -5021,7 +5021,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -5036,43 +5036,43 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -5089,7 +5089,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -5101,46 +5101,46 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>97.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="O10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5157,7 +5157,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -5169,46 +5169,46 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>97.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="O11">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5225,7 +5225,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -5237,19 +5237,19 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -5258,25 +5258,25 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5293,7 +5293,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -5305,19 +5305,19 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -5326,25 +5326,25 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5361,7 +5361,7 @@
         <v>50</v>
       </c>
       <c r="E14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -5376,43 +5376,43 @@
         <v>80</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5429,7 +5429,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -5441,46 +5441,46 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5497,7 +5497,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -5512,16 +5512,16 @@
         <v>95</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -5530,25 +5530,25 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5577,10 +5577,10 @@
         <v>33.3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -5589,34 +5589,34 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5633,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -5645,46 +5645,46 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5701,7 +5701,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -5713,19 +5713,19 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -5734,25 +5734,25 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5769,7 +5769,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -5784,16 +5784,16 @@
         <v>85</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -5802,25 +5802,25 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5837,7 +5837,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -5852,16 +5852,16 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -5870,25 +5870,25 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5905,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -5917,19 +5917,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -5938,25 +5938,25 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5973,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -5988,16 +5988,16 @@
         <v>90</v>
       </c>
       <c r="J23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -6006,25 +6006,25 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -6041,7 +6041,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -6053,19 +6053,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -6074,25 +6074,25 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6109,7 +6109,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>50</v>
@@ -6124,16 +6124,16 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -6145,16 +6145,16 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>90</v>
@@ -6189,46 +6189,46 @@
         <v>96.7</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N26">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6245,7 +6245,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -6260,43 +6260,43 @@
         <v>95</v>
       </c>
       <c r="J27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6313,7 +6313,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -6325,46 +6325,46 @@
         <v>96.7</v>
       </c>
       <c r="I28">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6381,7 +6381,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -6393,19 +6393,19 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -6414,25 +6414,25 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6449,7 +6449,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -6461,46 +6461,46 @@
         <v>96.7</v>
       </c>
       <c r="I30">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6517,7 +6517,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -6532,16 +6532,16 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -6550,25 +6550,25 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6585,7 +6585,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -6600,43 +6600,43 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6653,7 +6653,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -6668,16 +6668,16 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -6686,25 +6686,25 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6721,7 +6721,7 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -6736,16 +6736,16 @@
         <v>90</v>
       </c>
       <c r="J34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>100</v>
@@ -6754,25 +6754,25 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6789,7 +6789,7 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -6801,19 +6801,19 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="M35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -6822,25 +6822,25 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6857,7 +6857,7 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -6869,19 +6869,19 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>100</v>
@@ -6890,25 +6890,25 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6925,7 +6925,7 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6937,46 +6937,46 @@
         <v>96.7</v>
       </c>
       <c r="I37">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6993,7 +6993,7 @@
         <v>15</v>
       </c>
       <c r="E38">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>80</v>
@@ -7008,43 +7008,43 @@
         <v>75</v>
       </c>
       <c r="J38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>57.5</v>
       </c>
       <c r="L38">
-        <v>66.7</v>
+        <v>81.3</v>
       </c>
       <c r="M38">
-        <v>90</v>
+        <v>77.3</v>
       </c>
       <c r="N38">
-        <v>97.09999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="O38">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -7076,43 +7076,43 @@
         <v>75</v>
       </c>
       <c r="J39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>100</v>
       </c>
       <c r="L39">
-        <v>106.7</v>
+        <v>50</v>
       </c>
       <c r="M39">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="N39">
         <v>97.09999999999999</v>
       </c>
       <c r="O39">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7129,7 +7129,7 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -7141,46 +7141,46 @@
         <v>96.7</v>
       </c>
       <c r="I40">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7197,7 +7197,7 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -7209,46 +7209,46 @@
         <v>96.7</v>
       </c>
       <c r="I41">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N41">
         <v>100</v>
       </c>
       <c r="O41">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7265,7 +7265,7 @@
         <v>100</v>
       </c>
       <c r="E42">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F42">
         <v>100</v>
@@ -7277,46 +7277,46 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M42">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="N42">
         <v>100</v>
       </c>
       <c r="O42">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -7333,7 +7333,7 @@
         <v>100</v>
       </c>
       <c r="E43">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F43">
         <v>100</v>
@@ -7348,16 +7348,16 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N43">
         <v>100</v>
@@ -7366,25 +7366,25 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -7401,7 +7401,7 @@
         <v>100</v>
       </c>
       <c r="E44">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F44">
         <v>100</v>
@@ -7413,46 +7413,46 @@
         <v>100</v>
       </c>
       <c r="I44">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N44">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O44">
         <v>100</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="126">
   <si>
     <t>Materia</t>
   </si>
@@ -224,18 +224,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Mateos Sanchez Jorge</t>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,27 +248,27 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
     <t>FRANCO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>JUSTO</t>
   </si>
   <si>
@@ -302,67 +302,67 @@
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
     <t>ANA LAURA</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
+    <t>RUTH</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
     <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
@@ -946,10 +946,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -958,16 +958,16 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -982,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1035,10 +1035,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1047,16 +1047,16 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1124,10 +1124,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1136,10 +1136,10 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1213,10 +1213,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1225,10 +1225,10 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1246,7 +1246,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -1302,10 +1302,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1314,10 +1314,10 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1391,10 +1391,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1403,10 +1403,10 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1415,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1480,10 +1480,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1492,19 +1492,19 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <v>5</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1513,10 +1513,10 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1569,10 +1569,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1581,19 +1581,19 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1602,10 +1602,10 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1658,10 +1658,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1670,10 +1670,10 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1747,10 +1747,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1759,19 +1759,19 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1783,7 +1783,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1836,10 +1836,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1848,19 +1848,19 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>5</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1925,10 +1925,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1937,10 +1937,10 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1949,7 +1949,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2014,10 +2014,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2026,10 +2026,10 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2103,10 +2103,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2115,10 +2115,10 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2127,7 +2127,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2192,10 +2192,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2204,16 +2204,16 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2225,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2281,10 +2281,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2293,16 +2293,16 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2370,10 +2370,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2382,16 +2382,16 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2459,10 +2459,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2471,10 +2471,10 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2548,10 +2548,10 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2560,16 +2560,16 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2581,7 +2581,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2637,10 +2637,10 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2649,16 +2649,16 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>5</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2670,10 +2670,10 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2726,10 +2726,10 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2738,16 +2738,16 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2762,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2815,10 +2815,10 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2827,10 +2827,10 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2839,7 +2839,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -2904,10 +2904,10 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2916,19 +2916,19 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -2940,7 +2940,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2993,10 +2993,10 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3005,16 +3005,16 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -3082,10 +3082,10 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3094,19 +3094,19 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3118,7 +3118,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3171,10 +3171,10 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3183,19 +3183,19 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>5</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3207,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3260,10 +3260,10 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3272,10 +3272,10 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3284,7 +3284,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>5</v>
@@ -3296,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3349,10 +3349,10 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3361,16 +3361,16 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3438,10 +3438,10 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3450,10 +3450,10 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3462,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3527,10 +3527,10 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3539,10 +3539,10 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3551,7 +3551,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>9</v>
@@ -3563,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3616,10 +3616,10 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3628,19 +3628,19 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>7</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3652,7 +3652,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3705,10 +3705,10 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3717,19 +3717,19 @@
         <v>-1</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>5</v>
@@ -3738,7 +3738,7 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>8</v>
@@ -3794,10 +3794,10 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3806,10 +3806,10 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3818,7 +3818,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>9</v>
@@ -3883,10 +3883,10 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3895,10 +3895,10 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3972,10 +3972,10 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3984,10 +3984,10 @@
         <v>-1</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3996,7 +3996,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -4061,10 +4061,10 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4073,16 +4073,16 @@
         <v>-1</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>5</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -4094,7 +4094,7 @@
         <v>8</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>7</v>
@@ -4150,10 +4150,10 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4162,10 +4162,10 @@
         <v>-1</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W40">
         <v>6</v>
@@ -4174,7 +4174,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z40">
         <v>5</v>
@@ -4186,7 +4186,7 @@
         <v>10</v>
       </c>
       <c r="AC40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4239,10 +4239,10 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -4251,10 +4251,10 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>7</v>
@@ -4328,10 +4328,10 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4340,10 +4340,10 @@
         <v>-1</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -4361,10 +4361,10 @@
         <v>7</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC42">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -4417,10 +4417,10 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4429,16 +4429,16 @@
         <v>-1</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W43">
         <v>8</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4506,10 +4506,10 @@
         <v>-1</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -4518,10 +4518,10 @@
         <v>-1</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W44">
         <v>5</v>
@@ -4530,7 +4530,7 @@
         <v>8</v>
       </c>
       <c r="Y44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z44">
         <v>6</v>
@@ -4732,7 +4732,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4865,10 +4865,10 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="V6">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4933,10 +4933,10 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="V7">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -5001,7 +5001,7 @@
         <v>95.5</v>
       </c>
       <c r="U8">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -5069,7 +5069,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -5125,10 +5125,10 @@
         <v>82.5</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="S10">
         <v>75</v>
@@ -5137,10 +5137,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>94.3</v>
+        <v>62.9</v>
       </c>
       <c r="V10">
-        <v>98.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5193,10 +5193,10 @@
         <v>82.5</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="S11">
         <v>75</v>
@@ -5205,10 +5205,10 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>94.3</v>
+        <v>62.9</v>
       </c>
       <c r="V11">
-        <v>98.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5400,7 +5400,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -5412,7 +5412,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5480,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5601,7 +5601,7 @@
         <v>32.5</v>
       </c>
       <c r="Q17">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -5616,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="V17">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5684,7 +5684,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -6225,10 +6225,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="U26">
-        <v>97.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="V26">
-        <v>98.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6296,7 +6296,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6364,7 +6364,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6500,7 +6500,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6636,7 +6636,7 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6976,7 +6976,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -7032,7 +7032,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>57.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S38">
         <v>81.3</v>
@@ -7041,10 +7041,10 @@
         <v>77.3</v>
       </c>
       <c r="U38">
-        <v>48.6</v>
+        <v>51.4</v>
       </c>
       <c r="V38">
-        <v>80</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -7109,10 +7109,10 @@
         <v>95.5</v>
       </c>
       <c r="U39">
-        <v>97.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="V39">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7177,10 +7177,10 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="V40">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7248,7 +7248,7 @@
         <v>100</v>
       </c>
       <c r="V41">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7313,10 +7313,10 @@
         <v>95.5</v>
       </c>
       <c r="U42">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V42">
-        <v>98.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -7449,7 +7449,7 @@
         <v>100</v>
       </c>
       <c r="U44">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="V44">
         <v>100</v>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7582,19 +7582,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>90.2</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7608,25 +7608,25 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>41</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>90.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>9.800000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7637,28 +7637,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>41</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>92.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>7.3</v>
+        <v>14.6</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -7690,7 +7690,7 @@
         <v>7.3</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7710,19 +7710,19 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7772,7 +7772,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7804,16 +7804,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920298</v>
+        <v>21330051920337</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7827,16 +7827,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920298</v>
+        <v>21330051920337</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7850,16 +7850,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920337</v>
+        <v>21330051920301</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7873,22 +7873,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920337</v>
+        <v>21330051920301</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7905,7 +7905,7 @@
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7928,7 +7928,7 @@
         <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7951,7 +7951,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920293</v>
+        <v>21330051920291</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -7974,13 +7974,13 @@
         <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7988,16 +7988,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920299</v>
+        <v>21330051920293</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -8014,13 +8014,13 @@
         <v>21330051920300</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -8034,22 +8034,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920301</v>
+        <v>21330051920305</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920305</v>
+        <v>21330051920306</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8080,16 +8080,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B14" t="s">
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -8103,16 +8103,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -8126,16 +8126,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920307</v>
+        <v>21330051920090</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920090</v>
+        <v>21330051920313</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8172,22 +8172,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920313</v>
+        <v>21330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920315</v>
+        <v>21330051920316</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -8218,16 +8218,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920316</v>
+        <v>21330051920319</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -8241,22 +8241,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920319</v>
+        <v>21330051920323</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920323</v>
+        <v>21330051920326</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8287,47 +8287,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920326</v>
+        <v>21330051920330</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920330</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BLCM - Estadisticos 20222.xlsx
+++ b/grupos/4BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -230,12 +230,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,151 +248,70 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>FRANCO</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
     <t>MATA</t>
   </si>
   <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
-    <t>CRISTOPHER</t>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>RUTH</t>
   </si>
   <si>
     <t>LUIS CARLOS</t>
   </si>
   <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
     <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -943,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -952,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -964,7 +883,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -973,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1032,7 +951,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -1041,10 +960,10 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1053,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1062,10 +981,10 @@
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -1121,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1130,10 +1049,10 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1151,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1210,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1219,10 +1138,10 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1299,7 +1218,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1308,10 +1227,10 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1320,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1329,10 +1248,10 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>9</v>
@@ -1388,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1397,10 +1316,10 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1477,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1486,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1510,7 +1429,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1566,7 +1485,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1575,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -1587,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1599,7 +1518,7 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -1655,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1664,10 +1583,10 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1676,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1685,10 +1604,10 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1744,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1753,10 +1672,10 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1774,10 +1693,10 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1833,7 +1752,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1842,10 +1761,10 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1854,7 +1773,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1863,10 +1782,10 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1922,7 +1841,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1931,10 +1850,10 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1943,7 +1862,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -2011,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2020,10 +1939,10 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2044,7 +1963,7 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>9</v>
@@ -2100,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -2109,10 +2028,10 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -2189,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2198,10 +2117,10 @@
         <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2219,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>8</v>
@@ -2278,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2287,10 +2206,10 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2311,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>9</v>
@@ -2367,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2376,10 +2295,10 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2397,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2456,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2465,10 +2384,10 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2477,7 +2396,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2486,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2545,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2554,10 +2473,10 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2566,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2634,7 +2553,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2643,10 +2562,10 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2655,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2664,10 +2583,10 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2723,7 +2642,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2732,10 +2651,10 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2756,7 +2675,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2812,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>5</v>
@@ -2821,10 +2740,10 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2842,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2901,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2910,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>5</v>
@@ -2990,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2999,10 +2918,10 @@
         <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -3011,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -3023,7 +2942,7 @@
         <v>8</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>9</v>
@@ -3079,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -3088,10 +3007,10 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -3112,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3168,7 +3087,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>6</v>
@@ -3177,10 +3096,10 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -3189,7 +3108,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3198,10 +3117,10 @@
         <v>7</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>9</v>
@@ -3257,7 +3176,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -3266,10 +3185,10 @@
         <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -3287,10 +3206,10 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3346,7 +3265,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>9</v>
@@ -3355,10 +3274,10 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3379,7 +3298,7 @@
         <v>9</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>9</v>
@@ -3435,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3444,10 +3363,10 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -3465,10 +3384,10 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -3524,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3533,10 +3452,10 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3557,7 +3476,7 @@
         <v>9</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -3613,7 +3532,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -3622,10 +3541,10 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3634,7 +3553,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3643,10 +3562,10 @@
         <v>7</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>9</v>
@@ -3702,7 +3621,7 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>6</v>
@@ -3711,10 +3630,10 @@
         <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3791,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3800,10 +3719,10 @@
         <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>10</v>
@@ -3824,7 +3743,7 @@
         <v>9</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB36">
         <v>9</v>
@@ -3880,7 +3799,7 @@
         <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3889,10 +3808,10 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3910,10 +3829,10 @@
         <v>8</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB37">
         <v>9</v>
@@ -3969,7 +3888,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -3978,10 +3897,10 @@
         <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -4058,7 +3977,7 @@
         <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>6</v>
@@ -4067,10 +3986,10 @@
         <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -4088,10 +4007,10 @@
         <v>8</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB39">
         <v>7</v>
@@ -4147,7 +4066,7 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>9</v>
@@ -4156,10 +4075,10 @@
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -4177,10 +4096,10 @@
         <v>8</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB40">
         <v>10</v>
@@ -4236,7 +4155,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>10</v>
@@ -4245,10 +4164,10 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -4266,10 +4185,10 @@
         <v>8</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB41">
         <v>9</v>
@@ -4325,7 +4244,7 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>5</v>
@@ -4334,10 +4253,10 @@
         <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -4355,10 +4274,10 @@
         <v>8</v>
       </c>
       <c r="Z42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB42">
         <v>5</v>
@@ -4414,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
         <v>9</v>
@@ -4423,10 +4342,10 @@
         <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>10</v>
@@ -4435,7 +4354,7 @@
         <v>10</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -4447,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB43">
         <v>10</v>
@@ -4503,7 +4422,7 @@
         <v>7</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>8</v>
@@ -4512,10 +4431,10 @@
         <v>6</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U44">
         <v>6</v>
@@ -4536,7 +4455,7 @@
         <v>6</v>
       </c>
       <c r="AA44">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB44">
         <v>7</v>
@@ -4782,7 +4701,7 @@
         <v>96.7</v>
       </c>
       <c r="P5">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4850,7 +4769,7 @@
         <v>98.3</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4918,7 +4837,7 @@
         <v>95</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4986,7 +4905,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4998,7 +4917,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U8">
         <v>99</v>
@@ -5122,7 +5041,7 @@
         <v>98.3</v>
       </c>
       <c r="P10">
-        <v>82.5</v>
+        <v>51.6</v>
       </c>
       <c r="Q10">
         <v>68.8</v>
@@ -5131,10 +5050,10 @@
         <v>62.5</v>
       </c>
       <c r="S10">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="U10">
         <v>62.9</v>
@@ -5190,7 +5109,7 @@
         <v>98.3</v>
       </c>
       <c r="P11">
-        <v>82.5</v>
+        <v>51.6</v>
       </c>
       <c r="Q11">
         <v>68.8</v>
@@ -5199,10 +5118,10 @@
         <v>62.5</v>
       </c>
       <c r="S11">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="U11">
         <v>62.9</v>
@@ -5258,7 +5177,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -5326,7 +5245,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5394,7 +5313,7 @@
         <v>98.3</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5462,7 +5381,7 @@
         <v>66.7</v>
       </c>
       <c r="P15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5530,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -5598,7 +5517,7 @@
         <v>16.7</v>
       </c>
       <c r="P17">
-        <v>32.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q17">
         <v>31.3</v>
@@ -5610,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>34.1</v>
+        <v>23.4</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -5666,7 +5585,7 @@
         <v>98.3</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5734,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5802,7 +5721,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5938,7 +5857,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -6006,7 +5925,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -6074,7 +5993,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -6151,10 +6070,10 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T25">
-        <v>22.7</v>
+        <v>15.6</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -6210,7 +6129,7 @@
         <v>98.3</v>
       </c>
       <c r="P26">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -6222,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U26">
         <v>64.8</v>
@@ -6278,7 +6197,7 @@
         <v>98.3</v>
       </c>
       <c r="P27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -6346,7 +6265,7 @@
         <v>98.3</v>
       </c>
       <c r="P28">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6414,7 +6333,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -6482,7 +6401,7 @@
         <v>98.3</v>
       </c>
       <c r="P30">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6618,7 +6537,7 @@
         <v>98.3</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6754,7 +6673,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6822,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6831,7 +6750,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6890,7 +6809,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6958,7 +6877,7 @@
         <v>98.3</v>
       </c>
       <c r="P37">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -7026,7 +6945,7 @@
         <v>80</v>
       </c>
       <c r="P38">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -7035,10 +6954,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S38">
-        <v>81.3</v>
+        <v>54.2</v>
       </c>
       <c r="T38">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="U38">
         <v>51.4</v>
@@ -7094,7 +7013,7 @@
         <v>95</v>
       </c>
       <c r="P39">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -7103,10 +7022,10 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="T39">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U39">
         <v>95.2</v>
@@ -7162,7 +7081,7 @@
         <v>98.3</v>
       </c>
       <c r="P40">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -7171,7 +7090,7 @@
         <v>100</v>
       </c>
       <c r="S40">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -7230,7 +7149,7 @@
         <v>98.3</v>
       </c>
       <c r="P41">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -7298,7 +7217,7 @@
         <v>98.3</v>
       </c>
       <c r="P42">
-        <v>77.5</v>
+        <v>70.3</v>
       </c>
       <c r="Q42">
         <v>100</v>
@@ -7307,10 +7226,10 @@
         <v>100</v>
       </c>
       <c r="S42">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T42">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U42">
         <v>66.7</v>
@@ -7434,7 +7353,7 @@
         <v>100</v>
       </c>
       <c r="P44">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q44">
         <v>100</v>
@@ -7518,19 +7437,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>58.5</v>
+        <v>73.2</v>
       </c>
       <c r="G2" s="2">
-        <v>41.5</v>
+        <v>26.8</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7550,19 +7469,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>63.4</v>
+        <v>78</v>
       </c>
       <c r="G3" s="2">
-        <v>36.6</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7669,7 +7588,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7678,19 +7597,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>92.7</v>
+        <v>87.8</v>
       </c>
       <c r="G7" s="2">
-        <v>7.3</v>
+        <v>12.2</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7701,7 +7620,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7722,7 +7641,7 @@
         <v>7.3</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7772,7 +7691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7804,16 +7723,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920337</v>
+        <v>21330051920323</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7827,16 +7746,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920337</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7850,22 +7769,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920301</v>
+        <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7876,13 +7795,13 @@
         <v>21330051920301</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7896,22 +7815,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920321</v>
+        <v>21330051920305</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7919,22 +7838,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920321</v>
+        <v>21330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
         <v>95</v>
       </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7942,22 +7861,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920289</v>
+        <v>21330051920319</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
         <v>96</v>
       </c>
-      <c r="D8" t="s">
-        <v>111</v>
-      </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7965,22 +7884,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920291</v>
+        <v>21330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
         <v>97</v>
       </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7988,323 +7907,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920293</v>
+        <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
         <v>98</v>
       </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920300</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920305</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920306</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920235</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920307</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920090</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920313</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920315</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920316</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920319</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920323</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920326</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920330</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>
